--- a/source/25_Templates/AI_Security_Requirements_Traceability_Matrix.xlsx
+++ b/source/25_Templates/AI_Security_Requirements_Traceability_Matrix.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">RTM!$1:$5</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">RTM!$A$4:$AN$192</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">RTM!$A$4:$AN$193</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,12 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4466" uniqueCount="1134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4497" uniqueCount="1136">
   <si>
     <t xml:space="preserve">AI Security Requirements Traceability Matrix</t>
   </si>
   <si>
-    <t xml:space="preserve">Built from the AI Security Wiki (https://nachi065.github.io/AI-Security-Wiki/) on 29 October 2026. Version 1.2.</t>
+    <t xml:space="preserve">Built from the AI Security Wiki (https://nachi065.github.io/AI-Security-Wiki/) on 29 October 2026. Version 1.3.</t>
   </si>
   <si>
     <t xml:space="preserve">About</t>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">What this is</t>
   </si>
   <si>
-    <t xml:space="preserve">A requirements matrix for the security review of one AI system, built in-house or bought. It holds 188 requirements: each sentence of the Implementation Expectation of the wiki's 46 controls is one requirement, so every row traces to a control, the risks it treats, the wiki test cases and the framework and regional crosswalks.</t>
+    <t xml:space="preserve">A requirements matrix for the security review of one AI system, built in-house or bought. It holds 189 requirements: each sentence of the Implementation Expectation of the wiki's 46 controls is one requirement, so every row traces to a control, the risks it treats, the wiki test cases and the framework and regional crosswalks.</t>
   </si>
   <si>
     <t xml:space="preserve">Who fills what</t>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">RTM</t>
   </si>
   <si>
-    <t xml:space="preserve">188 requirements with scoping, vendor and assessor columns.</t>
+    <t xml:space="preserve">189 requirements with scoping, vendor and assessor columns.</t>
   </si>
   <si>
     <t xml:space="preserve">Dashboard</t>
@@ -252,7 +252,7 @@
     <t xml:space="preserve">AI Security Requirements Traceability Matrix Copyright (c) 2026 Nachiket Sathaye and Ankush Jain. Licensed under CC BY-SA 4.0 (https://creativecommons.org/licenses/by-sa/4.0/). See the License sheet for credit, ShareAlike and third-party terms.</t>
   </si>
   <si>
-    <t xml:space="preserve">AI Security Requirements Traceability Matrix, version 1.2, 29 October 2026</t>
+    <t xml:space="preserve">AI Security Requirements Traceability Matrix, version 1.3, 29 October 2026</t>
   </si>
   <si>
     <t xml:space="preserve">License notice</t>
@@ -2034,7 +2034,7 @@
     <t xml:space="preserve">Start a long-running test agent and stop it. Measure the time until no further actions occur and credentials are invalid. Sample high-risk use cases and confirm each has a kill switch, a fallback and a test within the last year; suspend one model in the lab and confirm decisions route to the fallback.</t>
   </si>
   <si>
-    <t xml:space="preserve">AI-R07, AI-R11, AI-R21, AI-R25</t>
+    <t xml:space="preserve">AI-R07, AI-R11, AI-R21, AI-R25, AI-R55</t>
   </si>
   <si>
     <t xml:space="preserve">MANAGE 2.4; MANAGE 2.3</t>
@@ -2169,7 +2169,7 @@
     <t xml:space="preserve">Have a test agent run code that tries to reach the network, read secrets and write outside its workspace. Confirm each attempt fails and is logged.</t>
   </si>
   <si>
-    <t xml:space="preserve">AI-R07, AI-R21, AI-R22, AI-R25</t>
+    <t xml:space="preserve">AI-R07, AI-R21, AI-R22, AI-R25, AI-R55</t>
   </si>
   <si>
     <t xml:space="preserve">A.4.5 System and computing resources; A.6.2.5 AI system deployment</t>
@@ -2478,7 +2478,7 @@
     <t xml:space="preserve">Sample production systems and confirm each has a current threat model, a control selection that matches its tier and a signed approval.</t>
   </si>
   <si>
-    <t xml:space="preserve">AI-R05, AI-R07, AI-R08, AI-R14, AI-R16</t>
+    <t xml:space="preserve">AI-R05, AI-R07, AI-R08, AI-R14, AI-R16, AI-R55</t>
   </si>
   <si>
     <t xml:space="preserve">MANAGE 1.1; GOVERN 4.2; MEASURE 2.7</t>
@@ -2709,7 +2709,7 @@
     <t xml:space="preserve">Sample accepted risks and confirm the approver had the authority. Let a test exception expire and confirm the technical control blocks the activity again.</t>
   </si>
   <si>
-    <t xml:space="preserve">AI-R02, AI-R18, AI-R28</t>
+    <t xml:space="preserve">AI-R02, AI-R18, AI-R28, AI-R55</t>
   </si>
   <si>
     <t xml:space="preserve">GOVERN 1.3; MAP 1.5; MANAGE 1.2; MANAGE 1.4</t>
@@ -2770,6 +2770,12 @@
   </si>
   <si>
     <t xml:space="preserve">Give every exception an owner, a compensating control and an expiry date that the technical control enforces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-CTRL-037.R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allow for attackers who use AI: set remediation and exception time limits for exposed systems on the assumption that a disclosed vulnerability can be exploited within days, and size vulnerability triage for a higher volume of findings (AI-R55).</t>
   </si>
   <si>
     <t xml:space="preserve">AI-CTRL-038.R1</t>
@@ -4882,8 +4888,8 @@
         <v>115</v>
       </c>
       <c r="B6" s="19" t="n">
-        <f aca="false">COUNTA(RTM!$A$5:$A$192)</f>
-        <v>188</v>
+        <f aca="false">COUNTA(RTM!$A$5:$A$193)</f>
+        <v>189</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4891,8 +4897,8 @@
         <v>116</v>
       </c>
       <c r="B7" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$AD$5:$AD$192,"Y")</f>
-        <v>188</v>
+        <f aca="false">COUNTIF(RTM!$AD$5:$AD$193,"Y")</f>
+        <v>189</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4900,7 +4906,7 @@
         <v>117</v>
       </c>
       <c r="B8" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>87</v>
       </c>
     </row>
@@ -4909,7 +4915,7 @@
         <v>118</v>
       </c>
       <c r="B9" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AF$5:$AF$192,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AF$5:$AF$193,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
@@ -4918,8 +4924,8 @@
         <v>119</v>
       </c>
       <c r="B10" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AF$5:$AF$192,"")</f>
-        <v>188</v>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AF$5:$AF$193,"")</f>
+        <v>189</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4927,7 +4933,7 @@
         <v>120</v>
       </c>
       <c r="B11" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AN$5:$AN$192,"No detail: treat as unanswered")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AN$5:$AN$193,"No detail: treat as unanswered")</f>
         <v>0</v>
       </c>
     </row>
@@ -4936,7 +4942,7 @@
         <v>121</v>
       </c>
       <c r="B12" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"&lt;&gt;Pending",RTM!$AJ$5:$AJ$192,"&lt;&gt;")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"&lt;&gt;Pending",RTM!$AJ$5:$AJ$193,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
@@ -4954,7 +4960,7 @@
         <v>123</v>
       </c>
       <c r="B14" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
     </row>
@@ -4981,11 +4987,11 @@
         <v>127</v>
       </c>
       <c r="B18" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending")</f>
-        <v>188</v>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending")</f>
+        <v>189</v>
       </c>
       <c r="C18" s="20" t="n">
-        <f aca="false">IFERROR(B18/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B18/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>1</v>
       </c>
     </row>
@@ -4994,11 +5000,11 @@
         <v>128</v>
       </c>
       <c r="B19" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="C19" s="20" t="n">
-        <f aca="false">IFERROR(B19/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B19/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5007,11 +5013,11 @@
         <v>129</v>
       </c>
       <c r="B20" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="C20" s="20" t="n">
-        <f aca="false">IFERROR(B20/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B20/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5020,11 +5026,11 @@
         <v>130</v>
       </c>
       <c r="B21" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="C21" s="20" t="n">
-        <f aca="false">IFERROR(B21/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B21/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5033,11 +5039,11 @@
         <v>131</v>
       </c>
       <c r="B22" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Not Applicable")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Not Applicable")</f>
         <v>0</v>
       </c>
       <c r="C22" s="20" t="n">
-        <f aca="false">IFERROR(B22/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B22/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5064,11 +5070,11 @@
         <v>134</v>
       </c>
       <c r="B26" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AF$5:$AF$192,"Yes")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AF$5:$AF$193,"Yes")</f>
         <v>0</v>
       </c>
       <c r="C26" s="20" t="n">
-        <f aca="false">IFERROR(B26/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B26/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5077,11 +5083,11 @@
         <v>135</v>
       </c>
       <c r="B27" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AF$5:$AF$192,"No")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AF$5:$AF$193,"No")</f>
         <v>0</v>
       </c>
       <c r="C27" s="20" t="n">
-        <f aca="false">IFERROR(B27/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B27/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5090,11 +5096,11 @@
         <v>136</v>
       </c>
       <c r="B28" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AF$5:$AF$192,"Partial")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AF$5:$AF$193,"Partial")</f>
         <v>0</v>
       </c>
       <c r="C28" s="20" t="n">
-        <f aca="false">IFERROR(B28/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B28/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5103,11 +5109,11 @@
         <v>137</v>
       </c>
       <c r="B29" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$192,"Y",RTM!$AF$5:$AF$192,"N/A")</f>
+        <f aca="false">COUNTIFS(RTM!$AD$5:$AD$193,"Y",RTM!$AF$5:$AF$193,"N/A")</f>
         <v>0</v>
       </c>
       <c r="C29" s="20" t="n">
-        <f aca="false">IFERROR(B29/COUNTIF(RTM!$AD$5:$AD$192,"Y"),0)</f>
+        <f aca="false">IFERROR(B29/COUNTIF(RTM!$AD$5:$AD$193,"Y"),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5154,31 +5160,31 @@
         <v>27</v>
       </c>
       <c r="B33" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$F$5:$F$192,"Discovery")</f>
+        <f aca="false">COUNTIF(RTM!$F$5:$F$193,"Discovery")</f>
         <v>20</v>
       </c>
       <c r="C33" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Discovery",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Discovery",RTM!$AD$5:$AD$193,"Y")</f>
         <v>20</v>
       </c>
       <c r="D33" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Discovery",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Discovery",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>18</v>
       </c>
       <c r="E33" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Discovery",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Discovery",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F33" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Discovery",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Discovery",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G33" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Discovery",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Discovery",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H33" s="20" t="n">
-        <f aca="false">IFERROR((C33-COUNTIFS(RTM!$F$5:$F$192,"Discovery",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C33,0)</f>
+        <f aca="false">IFERROR((C33-COUNTIFS(RTM!$F$5:$F$193,"Discovery",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C33,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5187,31 +5193,31 @@
         <v>29</v>
       </c>
       <c r="B34" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$F$5:$F$192,"Design")</f>
-        <v>33</v>
+        <f aca="false">COUNTIF(RTM!$F$5:$F$193,"Design")</f>
+        <v>34</v>
       </c>
       <c r="C34" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Design",RTM!$AD$5:$AD$192,"Y")</f>
-        <v>33</v>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Design",RTM!$AD$5:$AD$193,"Y")</f>
+        <v>34</v>
       </c>
       <c r="D34" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Design",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Design",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>11</v>
       </c>
       <c r="E34" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Design",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Design",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F34" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Design",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Design",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G34" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Design",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Design",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H34" s="20" t="n">
-        <f aca="false">IFERROR((C34-COUNTIFS(RTM!$F$5:$F$192,"Design",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C34,0)</f>
+        <f aca="false">IFERROR((C34-COUNTIFS(RTM!$F$5:$F$193,"Design",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C34,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5220,31 +5226,31 @@
         <v>31</v>
       </c>
       <c r="B35" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$F$5:$F$192,"Implementation")</f>
+        <f aca="false">COUNTIF(RTM!$F$5:$F$193,"Implementation")</f>
         <v>92</v>
       </c>
       <c r="C35" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Implementation",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Implementation",RTM!$AD$5:$AD$193,"Y")</f>
         <v>92</v>
       </c>
       <c r="D35" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Implementation",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Implementation",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>39</v>
       </c>
       <c r="E35" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Implementation",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Implementation",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F35" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Implementation",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Implementation",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G35" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Implementation",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Implementation",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H35" s="20" t="n">
-        <f aca="false">IFERROR((C35-COUNTIFS(RTM!$F$5:$F$192,"Implementation",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C35,0)</f>
+        <f aca="false">IFERROR((C35-COUNTIFS(RTM!$F$5:$F$193,"Implementation",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C35,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5253,31 +5259,31 @@
         <v>33</v>
       </c>
       <c r="B36" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$F$5:$F$192,"Platform")</f>
+        <f aca="false">COUNTIF(RTM!$F$5:$F$193,"Platform")</f>
         <v>22</v>
       </c>
       <c r="C36" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Platform",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Platform",RTM!$AD$5:$AD$193,"Y")</f>
         <v>22</v>
       </c>
       <c r="D36" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Platform",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Platform",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>8</v>
       </c>
       <c r="E36" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Platform",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Platform",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F36" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Platform",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Platform",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G36" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Platform",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Platform",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H36" s="20" t="n">
-        <f aca="false">IFERROR((C36-COUNTIFS(RTM!$F$5:$F$192,"Platform",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C36,0)</f>
+        <f aca="false">IFERROR((C36-COUNTIFS(RTM!$F$5:$F$193,"Platform",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C36,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5286,31 +5292,31 @@
         <v>35</v>
       </c>
       <c r="B37" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$F$5:$F$192,"Production")</f>
+        <f aca="false">COUNTIF(RTM!$F$5:$F$193,"Production")</f>
         <v>21</v>
       </c>
       <c r="C37" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Production",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Production",RTM!$AD$5:$AD$193,"Y")</f>
         <v>21</v>
       </c>
       <c r="D37" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Production",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Production",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>11</v>
       </c>
       <c r="E37" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Production",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Production",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F37" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Production",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Production",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G37" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$F$5:$F$192,"Production",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$F$5:$F$193,"Production",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H37" s="20" t="n">
-        <f aca="false">IFERROR((C37-COUNTIFS(RTM!$F$5:$F$192,"Production",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C37,0)</f>
+        <f aca="false">IFERROR((C37-COUNTIFS(RTM!$F$5:$F$193,"Production",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C37,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5357,31 +5363,31 @@
         <v>38</v>
       </c>
       <c r="B41" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$G$5:$G$192,"All")</f>
-        <v>172</v>
+        <f aca="false">COUNTIF(RTM!$G$5:$G$193,"All")</f>
+        <v>173</v>
       </c>
       <c r="C41" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"All",RTM!$AD$5:$AD$192,"Y")</f>
-        <v>172</v>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"All",RTM!$AD$5:$AD$193,"Y")</f>
+        <v>173</v>
       </c>
       <c r="D41" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"All",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"All",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>82</v>
       </c>
       <c r="E41" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"All",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"All",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F41" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"All",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"All",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G41" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"All",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"All",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H41" s="20" t="n">
-        <f aca="false">IFERROR((C41-COUNTIFS(RTM!$G$5:$G$192,"All",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C41,0)</f>
+        <f aca="false">IFERROR((C41-COUNTIFS(RTM!$G$5:$G$193,"All",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C41,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5390,31 +5396,31 @@
         <v>40</v>
       </c>
       <c r="B42" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$G$5:$G$192,"Cloud")</f>
+        <f aca="false">COUNTIF(RTM!$G$5:$G$193,"Cloud")</f>
         <v>7</v>
       </c>
       <c r="C42" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"Cloud",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"Cloud",RTM!$AD$5:$AD$193,"Y")</f>
         <v>7</v>
       </c>
       <c r="D42" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"Cloud",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"Cloud",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>5</v>
       </c>
       <c r="E42" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"Cloud",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"Cloud",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F42" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"Cloud",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"Cloud",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G42" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"Cloud",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"Cloud",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H42" s="20" t="n">
-        <f aca="false">IFERROR((C42-COUNTIFS(RTM!$G$5:$G$192,"Cloud",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C42,0)</f>
+        <f aca="false">IFERROR((C42-COUNTIFS(RTM!$G$5:$G$193,"Cloud",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C42,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5423,31 +5429,31 @@
         <v>42</v>
       </c>
       <c r="B43" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted")</f>
+        <f aca="false">COUNTIF(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted")</f>
         <v>9</v>
       </c>
       <c r="C43" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$193,"Y")</f>
         <v>9</v>
       </c>
       <c r="D43" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>0</v>
       </c>
       <c r="E43" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F43" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G43" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H43" s="20" t="n">
-        <f aca="false">IFERROR((C43-COUNTIFS(RTM!$G$5:$G$192,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C43,0)</f>
+        <f aca="false">IFERROR((C43-COUNTIFS(RTM!$G$5:$G$193,"PaaS/IaaS/Self-hosted",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C43,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5494,31 +5500,31 @@
         <v>147</v>
       </c>
       <c r="B47" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Agents and Tools")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Agents and Tools")</f>
         <v>27</v>
       </c>
       <c r="C47" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Agents and Tools",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Agents and Tools",RTM!$AD$5:$AD$193,"Y")</f>
         <v>27</v>
       </c>
       <c r="D47" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Agents and Tools",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Agents and Tools",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>21</v>
       </c>
       <c r="E47" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Agents and Tools",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Agents and Tools",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F47" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Agents and Tools",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Agents and Tools",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G47" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Agents and Tools",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Agents and Tools",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H47" s="20" t="n">
-        <f aca="false">IFERROR((C47-COUNTIFS(RTM!$D$5:$D$192,"Agents and Tools",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C47,0)</f>
+        <f aca="false">IFERROR((C47-COUNTIFS(RTM!$D$5:$D$193,"Agents and Tools",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C47,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5527,31 +5533,31 @@
         <v>148</v>
       </c>
       <c r="B48" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Application Runtime")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Application Runtime")</f>
         <v>15</v>
       </c>
       <c r="C48" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Application Runtime",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Application Runtime",RTM!$AD$5:$AD$193,"Y")</f>
         <v>15</v>
       </c>
       <c r="D48" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Application Runtime",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Application Runtime",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>8</v>
       </c>
       <c r="E48" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Application Runtime",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Application Runtime",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F48" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Application Runtime",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Application Runtime",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G48" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Application Runtime",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Application Runtime",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H48" s="20" t="n">
-        <f aca="false">IFERROR((C48-COUNTIFS(RTM!$D$5:$D$192,"Application Runtime",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C48,0)</f>
+        <f aca="false">IFERROR((C48-COUNTIFS(RTM!$D$5:$D$193,"Application Runtime",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C48,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5560,31 +5566,31 @@
         <v>149</v>
       </c>
       <c r="B49" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Assurance and Testing")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Assurance and Testing")</f>
         <v>22</v>
       </c>
       <c r="C49" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Assurance and Testing",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Assurance and Testing",RTM!$AD$5:$AD$193,"Y")</f>
         <v>22</v>
       </c>
       <c r="D49" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Assurance and Testing",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Assurance and Testing",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>4</v>
       </c>
       <c r="E49" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Assurance and Testing",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Assurance and Testing",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F49" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Assurance and Testing",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Assurance and Testing",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G49" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Assurance and Testing",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Assurance and Testing",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H49" s="20" t="n">
-        <f aca="false">IFERROR((C49-COUNTIFS(RTM!$D$5:$D$192,"Assurance and Testing",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C49,0)</f>
+        <f aca="false">IFERROR((C49-COUNTIFS(RTM!$D$5:$D$193,"Assurance and Testing",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C49,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5593,31 +5599,31 @@
         <v>150</v>
       </c>
       <c r="B50" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Cost and Abuse")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Cost and Abuse")</f>
         <v>3</v>
       </c>
       <c r="C50" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Cost and Abuse",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Cost and Abuse",RTM!$AD$5:$AD$193,"Y")</f>
         <v>3</v>
       </c>
       <c r="D50" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Cost and Abuse",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Cost and Abuse",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>3</v>
       </c>
       <c r="E50" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Cost and Abuse",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Cost and Abuse",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F50" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Cost and Abuse",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Cost and Abuse",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G50" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Cost and Abuse",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Cost and Abuse",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H50" s="20" t="n">
-        <f aca="false">IFERROR((C50-COUNTIFS(RTM!$D$5:$D$192,"Cost and Abuse",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C50,0)</f>
+        <f aca="false">IFERROR((C50-COUNTIFS(RTM!$D$5:$D$193,"Cost and Abuse",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C50,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5626,31 +5632,31 @@
         <v>151</v>
       </c>
       <c r="B51" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Data and Retrieval")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Data and Retrieval")</f>
         <v>15</v>
       </c>
       <c r="C51" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Data and Retrieval",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Data and Retrieval",RTM!$AD$5:$AD$193,"Y")</f>
         <v>15</v>
       </c>
       <c r="D51" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Data and Retrieval",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Data and Retrieval",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>10</v>
       </c>
       <c r="E51" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Data and Retrieval",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Data and Retrieval",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F51" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Data and Retrieval",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Data and Retrieval",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G51" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Data and Retrieval",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Data and Retrieval",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H51" s="20" t="n">
-        <f aca="false">IFERROR((C51-COUNTIFS(RTM!$D$5:$D$192,"Data and Retrieval",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C51,0)</f>
+        <f aca="false">IFERROR((C51-COUNTIFS(RTM!$D$5:$D$193,"Data and Retrieval",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C51,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5659,31 +5665,31 @@
         <v>152</v>
       </c>
       <c r="B52" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Detection and Response")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Detection and Response")</f>
         <v>9</v>
       </c>
       <c r="C52" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Detection and Response",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Detection and Response",RTM!$AD$5:$AD$193,"Y")</f>
         <v>9</v>
       </c>
       <c r="D52" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Detection and Response",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Detection and Response",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>7</v>
       </c>
       <c r="E52" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Detection and Response",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Detection and Response",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F52" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Detection and Response",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Detection and Response",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G52" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Detection and Response",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Detection and Response",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H52" s="20" t="n">
-        <f aca="false">IFERROR((C52-COUNTIFS(RTM!$D$5:$D$192,"Detection and Response",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C52,0)</f>
+        <f aca="false">IFERROR((C52-COUNTIFS(RTM!$D$5:$D$193,"Detection and Response",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C52,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5692,31 +5698,31 @@
         <v>153</v>
       </c>
       <c r="B53" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Discovery and Workforce AI Use")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Discovery and Workforce AI Use")</f>
         <v>12</v>
       </c>
       <c r="C53" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$193,"Y")</f>
         <v>12</v>
       </c>
       <c r="D53" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>6</v>
       </c>
       <c r="E53" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F53" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G53" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H53" s="20" t="n">
-        <f aca="false">IFERROR((C53-COUNTIFS(RTM!$D$5:$D$192,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C53,0)</f>
+        <f aca="false">IFERROR((C53-COUNTIFS(RTM!$D$5:$D$193,"Discovery and Workforce AI Use",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C53,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5725,31 +5731,31 @@
         <v>154</v>
       </c>
       <c r="B54" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Governance and Compliance")</f>
-        <v>48</v>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Governance and Compliance")</f>
+        <v>49</v>
       </c>
       <c r="C54" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Governance and Compliance",RTM!$AD$5:$AD$192,"Y")</f>
-        <v>48</v>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Governance and Compliance",RTM!$AD$5:$AD$193,"Y")</f>
+        <v>49</v>
       </c>
       <c r="D54" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Governance and Compliance",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Governance and Compliance",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>16</v>
       </c>
       <c r="E54" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Governance and Compliance",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Governance and Compliance",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F54" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Governance and Compliance",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Governance and Compliance",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G54" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Governance and Compliance",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Governance and Compliance",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H54" s="20" t="n">
-        <f aca="false">IFERROR((C54-COUNTIFS(RTM!$D$5:$D$192,"Governance and Compliance",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C54,0)</f>
+        <f aca="false">IFERROR((C54-COUNTIFS(RTM!$D$5:$D$193,"Governance and Compliance",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C54,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5758,31 +5764,31 @@
         <v>155</v>
       </c>
       <c r="B55" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Identity and Access")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Identity and Access")</f>
         <v>12</v>
       </c>
       <c r="C55" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Identity and Access",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Identity and Access",RTM!$AD$5:$AD$193,"Y")</f>
         <v>12</v>
       </c>
       <c r="D55" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Identity and Access",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Identity and Access",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>12</v>
       </c>
       <c r="E55" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Identity and Access",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Identity and Access",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F55" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Identity and Access",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Identity and Access",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G55" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Identity and Access",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Identity and Access",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H55" s="20" t="n">
-        <f aca="false">IFERROR((C55-COUNTIFS(RTM!$D$5:$D$192,"Identity and Access",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C55,0)</f>
+        <f aca="false">IFERROR((C55-COUNTIFS(RTM!$D$5:$D$193,"Identity and Access",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C55,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5791,31 +5797,31 @@
         <v>156</v>
       </c>
       <c r="B56" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Model, Training and Pipeline")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Model, Training and Pipeline")</f>
         <v>11</v>
       </c>
       <c r="C56" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Model, Training and Pipeline",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Model, Training and Pipeline",RTM!$AD$5:$AD$193,"Y")</f>
         <v>11</v>
       </c>
       <c r="D56" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Model, Training and Pipeline",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Model, Training and Pipeline",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>0</v>
       </c>
       <c r="E56" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Model, Training and Pipeline",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Model, Training and Pipeline",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F56" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Model, Training and Pipeline",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Model, Training and Pipeline",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G56" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Model, Training and Pipeline",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Model, Training and Pipeline",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H56" s="20" t="n">
-        <f aca="false">IFERROR((C56-COUNTIFS(RTM!$D$5:$D$192,"Model, Training and Pipeline",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C56,0)</f>
+        <f aca="false">IFERROR((C56-COUNTIFS(RTM!$D$5:$D$193,"Model, Training and Pipeline",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C56,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5824,31 +5830,31 @@
         <v>157</v>
       </c>
       <c r="B57" s="19" t="n">
-        <f aca="false">COUNTIF(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience")</f>
+        <f aca="false">COUNTIF(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience")</f>
         <v>14</v>
       </c>
       <c r="C57" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$193,"Y")</f>
         <v>14</v>
       </c>
       <c r="D57" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$192,"Y",RTM!$AE$5:$AE$192,"Y")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$193,"Y",RTM!$AE$5:$AE$193,"Y")</f>
         <v>0</v>
       </c>
       <c r="E57" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Accepted")</f>
         <v>0</v>
       </c>
       <c r="F57" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Gap")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Gap")</f>
         <v>0</v>
       </c>
       <c r="G57" s="19" t="n">
-        <f aca="false">COUNTIFS(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Risk Accepted")</f>
+        <f aca="false">COUNTIFS(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Risk Accepted")</f>
         <v>0</v>
       </c>
       <c r="H57" s="20" t="n">
-        <f aca="false">IFERROR((C57-COUNTIFS(RTM!$D$5:$D$192,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$192,"Y",RTM!$AJ$5:$AJ$192,"Pending"))/C57,0)</f>
+        <f aca="false">IFERROR((C57-COUNTIFS(RTM!$D$5:$D$193,"Supply Chain, Infrastructure and Resilience",RTM!$AD$5:$AD$193,"Y",RTM!$AJ$5:$AJ$193,"Pending"))/C57,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -5874,7 +5880,7 @@
     <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AN192"/>
+  <dimension ref="A1:AN193"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="1"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -18935,83 +18941,93 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="28" t="s">
         <v>914</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>915</v>
+        <v>888</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>916</v>
+        <v>889</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E146" s="29" t="s">
         <v>232</v>
       </c>
       <c r="F146" s="29" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G146" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>918</v>
+        <v>891</v>
       </c>
       <c r="J146" s="6" t="s">
-        <v>919</v>
+        <v>892</v>
       </c>
       <c r="K146" s="6" t="s">
-        <v>920</v>
+        <v>893</v>
       </c>
       <c r="L146" s="29" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M146" s="6" t="s">
-        <v>921</v>
+        <v>894</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>922</v>
+        <v>895</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>923</v>
+        <v>896</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>924</v>
+        <v>897</v>
       </c>
       <c r="Q146" s="6" t="s">
-        <v>925</v>
+        <v>898</v>
       </c>
       <c r="R146" s="6" t="s">
-        <v>633</v>
+        <v>899</v>
       </c>
       <c r="S146" s="6" t="s">
-        <v>926</v>
+        <v>900</v>
       </c>
       <c r="T146" s="6" t="s">
-        <v>927</v>
+        <v>901</v>
       </c>
       <c r="U146" s="6" t="s">
-        <v>928</v>
+        <v>902</v>
       </c>
       <c r="V146" s="6" t="s">
-        <v>929</v>
-      </c>
-      <c r="W146" s="6"/>
-      <c r="X146" s="6"/>
+        <v>903</v>
+      </c>
+      <c r="W146" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="X146" s="6" t="s">
+        <v>381</v>
+      </c>
       <c r="Y146" s="6" t="s">
-        <v>930</v>
-      </c>
-      <c r="Z146" s="6"/>
-      <c r="AA146" s="6"/>
-      <c r="AB146" s="6"/>
+        <v>382</v>
+      </c>
+      <c r="Z146" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="AA146" s="6" t="s">
+        <v>905</v>
+      </c>
+      <c r="AB146" s="6" t="s">
+        <v>906</v>
+      </c>
       <c r="AC146" s="6" t="s">
-        <v>331</v>
+        <v>907</v>
       </c>
       <c r="AD146" s="30" t="s">
         <v>208</v>
@@ -19036,13 +19052,13 @@
     </row>
     <row r="147" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="28" t="s">
-        <v>931</v>
+        <v>916</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>149</v>
@@ -19057,54 +19073,54 @@
         <v>38</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>932</v>
+        <v>919</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J147" s="6" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="K147" s="6" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="L147" s="29" t="n">
         <v>17</v>
       </c>
       <c r="M147" s="6" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="N147" s="6" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="O147" s="6" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="P147" s="6" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="Q147" s="6" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="R147" s="6" t="s">
         <v>633</v>
       </c>
       <c r="S147" s="6" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="T147" s="6" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="U147" s="6" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="V147" s="6" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="W147" s="6"/>
       <c r="X147" s="6"/>
       <c r="Y147" s="6" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="Z147" s="6"/>
       <c r="AA147" s="6"/>
@@ -19138,10 +19154,10 @@
         <v>933</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>149</v>
@@ -19159,51 +19175,51 @@
         <v>934</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J148" s="6" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="K148" s="6" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="L148" s="29" t="n">
         <v>17</v>
       </c>
       <c r="M148" s="6" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="Q148" s="6" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="R148" s="6" t="s">
         <v>633</v>
       </c>
       <c r="S148" s="6" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="T148" s="6" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="U148" s="6" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="V148" s="6" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="W148" s="6"/>
       <c r="X148" s="6"/>
       <c r="Y148" s="6" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="Z148" s="6"/>
       <c r="AA148" s="6"/>
@@ -19237,10 +19253,10 @@
         <v>935</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>149</v>
@@ -19258,51 +19274,51 @@
         <v>936</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="J149" s="6" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="K149" s="6" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="L149" s="29" t="n">
         <v>17</v>
       </c>
       <c r="M149" s="6" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="N149" s="6" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="O149" s="6" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="P149" s="6" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="Q149" s="6" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="R149" s="6" t="s">
         <v>633</v>
       </c>
       <c r="S149" s="6" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="T149" s="6" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="U149" s="6" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="V149" s="6" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="W149" s="6"/>
       <c r="X149" s="6"/>
       <c r="Y149" s="6" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="Z149" s="6"/>
       <c r="AA149" s="6"/>
@@ -19331,93 +19347,83 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="28" t="s">
         <v>937</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>938</v>
+        <v>917</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>939</v>
+        <v>918</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E150" s="29" t="s">
         <v>232</v>
       </c>
       <c r="F150" s="29" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G150" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>941</v>
+        <v>920</v>
       </c>
       <c r="J150" s="6" t="s">
-        <v>942</v>
+        <v>921</v>
       </c>
       <c r="K150" s="6" t="s">
-        <v>943</v>
+        <v>922</v>
       </c>
       <c r="L150" s="29" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M150" s="6" t="s">
-        <v>944</v>
+        <v>923</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>945</v>
+        <v>924</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>946</v>
+        <v>925</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>947</v>
+        <v>926</v>
       </c>
       <c r="Q150" s="6" t="s">
-        <v>948</v>
+        <v>927</v>
       </c>
       <c r="R150" s="6" t="s">
-        <v>949</v>
+        <v>633</v>
       </c>
       <c r="S150" s="6" t="s">
-        <v>950</v>
+        <v>928</v>
       </c>
       <c r="T150" s="6" t="s">
-        <v>951</v>
+        <v>929</v>
       </c>
       <c r="U150" s="6" t="s">
-        <v>952</v>
+        <v>930</v>
       </c>
       <c r="V150" s="6" t="s">
-        <v>953</v>
-      </c>
-      <c r="W150" s="6" t="s">
-        <v>954</v>
-      </c>
-      <c r="X150" s="6" t="s">
-        <v>461</v>
-      </c>
+        <v>931</v>
+      </c>
+      <c r="W150" s="6"/>
+      <c r="X150" s="6"/>
       <c r="Y150" s="6" t="s">
-        <v>955</v>
-      </c>
-      <c r="Z150" s="6" t="s">
-        <v>956</v>
-      </c>
-      <c r="AA150" s="6" t="s">
-        <v>957</v>
-      </c>
-      <c r="AB150" s="6" t="s">
-        <v>958</v>
-      </c>
+        <v>932</v>
+      </c>
+      <c r="Z150" s="6"/>
+      <c r="AA150" s="6"/>
+      <c r="AB150" s="6"/>
       <c r="AC150" s="6" t="s">
-        <v>584</v>
+        <v>331</v>
       </c>
       <c r="AD150" s="30" t="s">
         <v>208</v>
@@ -19442,13 +19448,13 @@
     </row>
     <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="28" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>148</v>
@@ -19463,67 +19469,67 @@
         <v>38</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>960</v>
+        <v>942</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="J151" s="6" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="K151" s="6" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="L151" s="29" t="n">
         <v>9</v>
       </c>
       <c r="M151" s="6" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="N151" s="6" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="O151" s="6" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="P151" s="6" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="Q151" s="6" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="R151" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="S151" s="6" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="T151" s="6" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="U151" s="6" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="V151" s="6" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="W151" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X151" s="6" t="s">
         <v>461</v>
       </c>
       <c r="Y151" s="6" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="Z151" s="6" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="AA151" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB151" s="6" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AC151" s="6" t="s">
         <v>584</v>
@@ -19554,10 +19560,10 @@
         <v>961</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>148</v>
@@ -19575,64 +19581,64 @@
         <v>962</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="J152" s="6" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="K152" s="6" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="L152" s="29" t="n">
         <v>9</v>
       </c>
       <c r="M152" s="6" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="Q152" s="6" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="R152" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="S152" s="6" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="T152" s="6" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="U152" s="6" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="V152" s="6" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="W152" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X152" s="6" t="s">
         <v>461</v>
       </c>
       <c r="Y152" s="6" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="Z152" s="6" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="AA152" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB152" s="6" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AC152" s="6" t="s">
         <v>584</v>
@@ -19663,10 +19669,10 @@
         <v>963</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>148</v>
@@ -19684,64 +19690,64 @@
         <v>964</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="J153" s="6" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="K153" s="6" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="L153" s="29" t="n">
         <v>9</v>
       </c>
       <c r="M153" s="6" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="N153" s="6" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="O153" s="6" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="Q153" s="6" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="R153" s="6" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="S153" s="6" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="T153" s="6" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="U153" s="6" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="V153" s="6" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="W153" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X153" s="6" t="s">
         <v>461</v>
       </c>
       <c r="Y153" s="6" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="Z153" s="6" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="AA153" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB153" s="6" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="AC153" s="6" t="s">
         <v>584</v>
@@ -19767,71 +19773,93 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="28" t="s">
         <v>965</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>966</v>
+        <v>940</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>967</v>
+        <v>941</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="E154" s="29" t="s">
         <v>232</v>
       </c>
       <c r="F154" s="29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G154" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="I154" s="6" t="s">
-        <v>969</v>
+        <v>943</v>
       </c>
       <c r="J154" s="6" t="s">
-        <v>970</v>
+        <v>944</v>
       </c>
       <c r="K154" s="6" t="s">
-        <v>971</v>
+        <v>945</v>
       </c>
       <c r="L154" s="29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M154" s="6" t="s">
-        <v>972</v>
+        <v>946</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>973</v>
+        <v>947</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>974</v>
+        <v>948</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>975</v>
-      </c>
-      <c r="Q154" s="6"/>
-      <c r="R154" s="6"/>
-      <c r="S154" s="6"/>
-      <c r="T154" s="6"/>
-      <c r="U154" s="6"/>
+        <v>949</v>
+      </c>
+      <c r="Q154" s="6" t="s">
+        <v>950</v>
+      </c>
+      <c r="R154" s="6" t="s">
+        <v>951</v>
+      </c>
+      <c r="S154" s="6" t="s">
+        <v>952</v>
+      </c>
+      <c r="T154" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="U154" s="6" t="s">
+        <v>954</v>
+      </c>
       <c r="V154" s="6" t="s">
-        <v>976</v>
-      </c>
-      <c r="W154" s="6"/>
-      <c r="X154" s="6"/>
-      <c r="Y154" s="6"/>
-      <c r="Z154" s="6"/>
-      <c r="AA154" s="6"/>
-      <c r="AB154" s="6"/>
+        <v>955</v>
+      </c>
+      <c r="W154" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="X154" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="Y154" s="6" t="s">
+        <v>957</v>
+      </c>
+      <c r="Z154" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="AA154" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="AB154" s="6" t="s">
+        <v>960</v>
+      </c>
       <c r="AC154" s="6" t="s">
-        <v>331</v>
+        <v>584</v>
       </c>
       <c r="AD154" s="30" t="s">
         <v>208</v>
@@ -19856,13 +19884,13 @@
     </row>
     <row r="155" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="28" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>157</v>
@@ -19877,31 +19905,31 @@
         <v>38</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>978</v>
+        <v>970</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="J155" s="6" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="K155" s="6" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="L155" s="29" t="n">
         <v>14</v>
       </c>
       <c r="M155" s="6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="N155" s="6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="O155" s="6" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="Q155" s="6"/>
       <c r="R155" s="6"/>
@@ -19909,7 +19937,7 @@
       <c r="T155" s="6"/>
       <c r="U155" s="6"/>
       <c r="V155" s="6" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="W155" s="6"/>
       <c r="X155" s="6"/>
@@ -19946,10 +19974,10 @@
         <v>979</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>157</v>
@@ -19967,28 +19995,28 @@
         <v>980</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="J156" s="6" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="K156" s="6" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="L156" s="29" t="n">
         <v>14</v>
       </c>
       <c r="M156" s="6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -19996,7 +20024,7 @@
       <c r="T156" s="6"/>
       <c r="U156" s="6"/>
       <c r="V156" s="6" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="W156" s="6"/>
       <c r="X156" s="6"/>
@@ -20033,10 +20061,10 @@
         <v>981</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>157</v>
@@ -20054,28 +20082,28 @@
         <v>982</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="J157" s="6" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="K157" s="6" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="L157" s="29" t="n">
         <v>14</v>
       </c>
       <c r="M157" s="6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="N157" s="6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="O157" s="6" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="Q157" s="6"/>
       <c r="R157" s="6"/>
@@ -20083,7 +20111,7 @@
       <c r="T157" s="6"/>
       <c r="U157" s="6"/>
       <c r="V157" s="6" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="W157" s="6"/>
       <c r="X157" s="6"/>
@@ -20120,10 +20148,10 @@
         <v>983</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>157</v>
@@ -20141,28 +20169,28 @@
         <v>984</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="J158" s="6" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="K158" s="6" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="L158" s="29" t="n">
         <v>14</v>
       </c>
       <c r="M158" s="6" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -20170,7 +20198,7 @@
       <c r="T158" s="6"/>
       <c r="U158" s="6"/>
       <c r="V158" s="6" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="W158" s="6"/>
       <c r="X158" s="6"/>
@@ -20207,86 +20235,66 @@
         <v>985</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>987</v>
+        <v>969</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E159" s="29" t="s">
         <v>232</v>
       </c>
       <c r="F159" s="29" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G159" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>989</v>
+        <v>971</v>
       </c>
       <c r="J159" s="6" t="s">
-        <v>990</v>
+        <v>972</v>
       </c>
       <c r="K159" s="6" t="s">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="L159" s="29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M159" s="6" t="s">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="N159" s="6" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="O159" s="6" t="s">
-        <v>994</v>
+        <v>976</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>995</v>
-      </c>
-      <c r="Q159" s="6" t="s">
-        <v>996</v>
-      </c>
+        <v>977</v>
+      </c>
+      <c r="Q159" s="6"/>
       <c r="R159" s="6"/>
-      <c r="S159" s="6" t="s">
-        <v>997</v>
-      </c>
-      <c r="T159" s="6" t="s">
-        <v>998</v>
-      </c>
-      <c r="U159" s="6" t="s">
-        <v>999</v>
-      </c>
+      <c r="S159" s="6"/>
+      <c r="T159" s="6"/>
+      <c r="U159" s="6"/>
       <c r="V159" s="6" t="s">
-        <v>1000</v>
-      </c>
-      <c r="W159" s="6" t="s">
-        <v>954</v>
-      </c>
-      <c r="X159" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="Y159" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="Z159" s="6" t="s">
-        <v>904</v>
-      </c>
-      <c r="AA159" s="6" t="s">
-        <v>957</v>
-      </c>
-      <c r="AB159" s="6" t="s">
-        <v>641</v>
-      </c>
+        <v>978</v>
+      </c>
+      <c r="W159" s="6"/>
+      <c r="X159" s="6"/>
+      <c r="Y159" s="6"/>
+      <c r="Z159" s="6"/>
+      <c r="AA159" s="6"/>
+      <c r="AB159" s="6"/>
       <c r="AC159" s="6" t="s">
-        <v>1001</v>
+        <v>331</v>
       </c>
       <c r="AD159" s="30" t="s">
         <v>208</v>
@@ -20311,13 +20319,13 @@
     </row>
     <row r="160" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="28" t="s">
-        <v>1002</v>
+        <v>987</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>149</v>
@@ -20332,50 +20340,50 @@
         <v>38</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="I160" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J160" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K160" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L160" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M160" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q160" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R160" s="6"/>
       <c r="S160" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T160" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U160" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V160" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W160" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X160" s="6" t="s">
         <v>381</v>
@@ -20387,13 +20395,13 @@
         <v>904</v>
       </c>
       <c r="AA160" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB160" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC160" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD160" s="30" t="s">
         <v>208</v>
@@ -20421,10 +20429,10 @@
         <v>1004</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>149</v>
@@ -20442,47 +20450,47 @@
         <v>1005</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J161" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K161" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L161" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M161" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N161" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O161" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q161" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R161" s="6"/>
       <c r="S161" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T161" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U161" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V161" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W161" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X161" s="6" t="s">
         <v>381</v>
@@ -20494,13 +20502,13 @@
         <v>904</v>
       </c>
       <c r="AA161" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB161" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC161" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD161" s="30" t="s">
         <v>208</v>
@@ -20528,10 +20536,10 @@
         <v>1006</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>149</v>
@@ -20549,47 +20557,47 @@
         <v>1007</v>
       </c>
       <c r="I162" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J162" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K162" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L162" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M162" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q162" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R162" s="6"/>
       <c r="S162" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T162" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U162" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V162" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W162" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X162" s="6" t="s">
         <v>381</v>
@@ -20601,13 +20609,13 @@
         <v>904</v>
       </c>
       <c r="AA162" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB162" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC162" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD162" s="30" t="s">
         <v>208</v>
@@ -20635,10 +20643,10 @@
         <v>1008</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>149</v>
@@ -20656,47 +20664,47 @@
         <v>1009</v>
       </c>
       <c r="I163" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J163" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K163" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L163" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M163" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N163" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O163" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q163" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R163" s="6"/>
       <c r="S163" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T163" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U163" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V163" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W163" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X163" s="6" t="s">
         <v>381</v>
@@ -20708,13 +20716,13 @@
         <v>904</v>
       </c>
       <c r="AA163" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB163" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC163" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD163" s="30" t="s">
         <v>208</v>
@@ -20742,10 +20750,10 @@
         <v>1010</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>149</v>
@@ -20763,47 +20771,47 @@
         <v>1011</v>
       </c>
       <c r="I164" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J164" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K164" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L164" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M164" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q164" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R164" s="6"/>
       <c r="S164" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T164" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U164" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V164" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W164" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X164" s="6" t="s">
         <v>381</v>
@@ -20815,13 +20823,13 @@
         <v>904</v>
       </c>
       <c r="AA164" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB164" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC164" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD164" s="30" t="s">
         <v>208</v>
@@ -20849,10 +20857,10 @@
         <v>1012</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>149</v>
@@ -20870,47 +20878,47 @@
         <v>1013</v>
       </c>
       <c r="I165" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J165" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K165" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L165" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N165" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O165" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P165" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q165" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R165" s="6"/>
       <c r="S165" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T165" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U165" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V165" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W165" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X165" s="6" t="s">
         <v>381</v>
@@ -20922,13 +20930,13 @@
         <v>904</v>
       </c>
       <c r="AA165" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB165" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC165" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD165" s="30" t="s">
         <v>208</v>
@@ -20956,10 +20964,10 @@
         <v>1014</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>149</v>
@@ -20977,47 +20985,47 @@
         <v>1015</v>
       </c>
       <c r="I166" s="6" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="J166" s="6" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="K166" s="6" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="L166" s="29" t="n">
         <v>7</v>
       </c>
       <c r="M166" s="6" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="Q166" s="6" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="R166" s="6"/>
       <c r="S166" s="6" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="T166" s="6" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="U166" s="6" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="V166" s="6" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="W166" s="6" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="X166" s="6" t="s">
         <v>381</v>
@@ -21029,13 +21037,13 @@
         <v>904</v>
       </c>
       <c r="AA166" s="6" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="AB166" s="6" t="s">
         <v>641</v>
       </c>
       <c r="AC166" s="6" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="AD166" s="30" t="s">
         <v>208</v>
@@ -21058,70 +21066,92 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="28" t="s">
         <v>1016</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>1017</v>
+        <v>988</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>1018</v>
+        <v>989</v>
       </c>
       <c r="D167" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E167" s="29" t="s">
         <v>232</v>
       </c>
       <c r="F167" s="29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G167" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H167" s="6" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="I167" s="6" t="s">
-        <v>1020</v>
+        <v>991</v>
       </c>
       <c r="J167" s="6" t="s">
-        <v>1021</v>
+        <v>992</v>
       </c>
       <c r="K167" s="6" t="s">
-        <v>1022</v>
+        <v>993</v>
       </c>
       <c r="L167" s="29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M167" s="6" t="s">
-        <v>1023</v>
+        <v>994</v>
       </c>
       <c r="N167" s="6" t="s">
-        <v>1024</v>
+        <v>995</v>
       </c>
       <c r="O167" s="6" t="s">
-        <v>1025</v>
+        <v>996</v>
       </c>
       <c r="P167" s="6" t="s">
-        <v>1026</v>
-      </c>
-      <c r="Q167" s="6"/>
+        <v>997</v>
+      </c>
+      <c r="Q167" s="6" t="s">
+        <v>998</v>
+      </c>
       <c r="R167" s="6"/>
       <c r="S167" s="6" t="s">
-        <v>1027</v>
-      </c>
-      <c r="T167" s="6"/>
-      <c r="U167" s="6"/>
-      <c r="V167" s="6"/>
-      <c r="W167" s="6"/>
-      <c r="X167" s="6"/>
-      <c r="Y167" s="6"/>
-      <c r="Z167" s="6"/>
-      <c r="AA167" s="6"/>
-      <c r="AB167" s="6"/>
-      <c r="AC167" s="6"/>
+        <v>999</v>
+      </c>
+      <c r="T167" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="U167" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="V167" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="W167" s="6" t="s">
+        <v>956</v>
+      </c>
+      <c r="X167" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="Y167" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="Z167" s="6" t="s">
+        <v>904</v>
+      </c>
+      <c r="AA167" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="AB167" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="AC167" s="6" t="s">
+        <v>1003</v>
+      </c>
       <c r="AD167" s="30" t="s">
         <v>208</v>
       </c>
@@ -21145,13 +21175,13 @@
     </row>
     <row r="168" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="28" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>154</v>
@@ -21166,36 +21196,36 @@
         <v>38</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>1029</v>
+        <v>1021</v>
       </c>
       <c r="I168" s="6" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="J168" s="6" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="K168" s="6" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="L168" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M168" s="6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
       <c r="S168" s="6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="T168" s="6"/>
       <c r="U168" s="6"/>
@@ -21233,10 +21263,10 @@
         <v>1030</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>154</v>
@@ -21254,33 +21284,33 @@
         <v>1031</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="J169" s="6" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="K169" s="6" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="L169" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M169" s="6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N169" s="6" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="O169" s="6" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="Q169" s="6"/>
       <c r="R169" s="6"/>
       <c r="S169" s="6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="T169" s="6"/>
       <c r="U169" s="6"/>
@@ -21318,10 +21348,10 @@
         <v>1032</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>154</v>
@@ -21339,33 +21369,33 @@
         <v>1033</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="J170" s="6" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="K170" s="6" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="L170" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M170" s="6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
       <c r="S170" s="6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="T170" s="6"/>
       <c r="U170" s="6"/>
@@ -21403,10 +21433,10 @@
         <v>1034</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>154</v>
@@ -21424,33 +21454,33 @@
         <v>1035</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="J171" s="6" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="K171" s="6" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="L171" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M171" s="6" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N171" s="6" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="O171" s="6" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="Q171" s="6"/>
       <c r="R171" s="6"/>
       <c r="S171" s="6" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="T171" s="6"/>
       <c r="U171" s="6"/>
@@ -21483,15 +21513,15 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="28" t="s">
         <v>1036</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>1037</v>
+        <v>1019</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>1038</v>
+        <v>1020</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>154</v>
@@ -21500,41 +21530,43 @@
         <v>232</v>
       </c>
       <c r="F172" s="29" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="G172" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="I172" s="6" t="s">
-        <v>1040</v>
+        <v>1022</v>
       </c>
       <c r="J172" s="6" t="s">
-        <v>1041</v>
+        <v>1023</v>
       </c>
       <c r="K172" s="6" t="s">
-        <v>1042</v>
+        <v>1024</v>
       </c>
       <c r="L172" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M172" s="6" t="s">
-        <v>1043</v>
+        <v>1025</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>1045</v>
+        <v>1027</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
-      <c r="S172" s="6"/>
+      <c r="S172" s="6" t="s">
+        <v>1029</v>
+      </c>
       <c r="T172" s="6"/>
       <c r="U172" s="6"/>
       <c r="V172" s="6"/>
@@ -21568,13 +21600,13 @@
     </row>
     <row r="173" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="28" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>154</v>
@@ -21589,31 +21621,31 @@
         <v>38</v>
       </c>
       <c r="H173" s="6" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J173" s="6" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K173" s="6" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="L173" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M173" s="6" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N173" s="6" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="O173" s="6" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="Q173" s="6"/>
       <c r="R173" s="6"/>
@@ -21654,10 +21686,10 @@
         <v>1049</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>154</v>
@@ -21675,28 +21707,28 @@
         <v>1050</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J174" s="6" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K174" s="6" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="L174" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M174" s="6" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -21737,10 +21769,10 @@
         <v>1051</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>154</v>
@@ -21758,28 +21790,28 @@
         <v>1052</v>
       </c>
       <c r="I175" s="6" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="J175" s="6" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="K175" s="6" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="L175" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M175" s="6" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="N175" s="6" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="O175" s="6" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="P175" s="6" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="Q175" s="6"/>
       <c r="R175" s="6"/>
@@ -21815,15 +21847,15 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="28" t="s">
         <v>1053</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>1055</v>
+        <v>1040</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>154</v>
@@ -21832,55 +21864,51 @@
         <v>232</v>
       </c>
       <c r="F176" s="29" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G176" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="J176" s="6" t="s">
-        <v>1058</v>
+        <v>1043</v>
       </c>
       <c r="K176" s="6" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="L176" s="29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M176" s="6" t="s">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>1061</v>
+        <v>1046</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
       <c r="S176" s="6"/>
       <c r="T176" s="6"/>
       <c r="U176" s="6"/>
-      <c r="V176" s="6" t="s">
-        <v>1064</v>
-      </c>
+      <c r="V176" s="6"/>
       <c r="W176" s="6"/>
       <c r="X176" s="6"/>
       <c r="Y176" s="6"/>
       <c r="Z176" s="6"/>
       <c r="AA176" s="6"/>
       <c r="AB176" s="6"/>
-      <c r="AC176" s="6" t="s">
-        <v>1065</v>
-      </c>
+      <c r="AC176" s="6"/>
       <c r="AD176" s="30" t="s">
         <v>208</v>
       </c>
@@ -21904,13 +21932,13 @@
     </row>
     <row r="177" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="28" t="s">
-        <v>1066</v>
+        <v>1055</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>154</v>
@@ -21925,31 +21953,31 @@
         <v>38</v>
       </c>
       <c r="H177" s="6" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
       <c r="I177" s="6" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="J177" s="6" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="K177" s="6" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="L177" s="29" t="n">
         <v>3</v>
       </c>
       <c r="M177" s="6" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="N177" s="6" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="O177" s="6" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="P177" s="6" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="Q177" s="6"/>
       <c r="R177" s="6"/>
@@ -21957,7 +21985,7 @@
       <c r="T177" s="6"/>
       <c r="U177" s="6"/>
       <c r="V177" s="6" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="W177" s="6"/>
       <c r="X177" s="6"/>
@@ -21966,7 +21994,7 @@
       <c r="AA177" s="6"/>
       <c r="AB177" s="6"/>
       <c r="AC177" s="6" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="AD177" s="30" t="s">
         <v>208</v>
@@ -21994,10 +22022,10 @@
         <v>1068</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>154</v>
@@ -22015,28 +22043,28 @@
         <v>1069</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="J178" s="6" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="K178" s="6" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="L178" s="29" t="n">
         <v>3</v>
       </c>
       <c r="M178" s="6" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -22044,7 +22072,7 @@
       <c r="T178" s="6"/>
       <c r="U178" s="6"/>
       <c r="V178" s="6" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="W178" s="6"/>
       <c r="X178" s="6"/>
@@ -22053,7 +22081,7 @@
       <c r="AA178" s="6"/>
       <c r="AB178" s="6"/>
       <c r="AC178" s="6" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="AD178" s="30" t="s">
         <v>208</v>
@@ -22081,10 +22109,10 @@
         <v>1070</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>154</v>
@@ -22102,28 +22130,28 @@
         <v>1071</v>
       </c>
       <c r="I179" s="6" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="J179" s="6" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="K179" s="6" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="L179" s="29" t="n">
         <v>3</v>
       </c>
       <c r="M179" s="6" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="N179" s="6" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="O179" s="6" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="Q179" s="6"/>
       <c r="R179" s="6"/>
@@ -22131,7 +22159,7 @@
       <c r="T179" s="6"/>
       <c r="U179" s="6"/>
       <c r="V179" s="6" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="W179" s="6"/>
       <c r="X179" s="6"/>
@@ -22140,7 +22168,7 @@
       <c r="AA179" s="6"/>
       <c r="AB179" s="6"/>
       <c r="AC179" s="6" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="AD179" s="30" t="s">
         <v>208</v>
@@ -22163,15 +22191,15 @@
         <v>Awaiting response</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="28" t="s">
         <v>1072</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>1073</v>
+        <v>1056</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>1074</v>
+        <v>1057</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>154</v>
@@ -22180,47 +22208,45 @@
         <v>232</v>
       </c>
       <c r="F180" s="29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G180" s="29" t="s">
         <v>38</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="I180" s="6" t="s">
-        <v>1076</v>
+        <v>1059</v>
       </c>
       <c r="J180" s="6" t="s">
-        <v>1077</v>
+        <v>1060</v>
       </c>
       <c r="K180" s="6" t="s">
-        <v>1078</v>
+        <v>1061</v>
       </c>
       <c r="L180" s="29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M180" s="6" t="s">
-        <v>628</v>
+        <v>1062</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>629</v>
+        <v>1063</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>630</v>
+        <v>1064</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>1079</v>
+        <v>1065</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
       <c r="S180" s="6"/>
       <c r="T180" s="6"/>
-      <c r="U180" s="6" t="s">
-        <v>673</v>
-      </c>
+      <c r="U180" s="6"/>
       <c r="V180" s="6" t="s">
-        <v>1080</v>
+        <v>1066</v>
       </c>
       <c r="W180" s="6"/>
       <c r="X180" s="6"/>
@@ -22229,7 +22255,7 @@
       <c r="AA180" s="6"/>
       <c r="AB180" s="6"/>
       <c r="AC180" s="6" t="s">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="AD180" s="30" t="s">
         <v>208</v>
@@ -22254,13 +22280,13 @@
     </row>
     <row r="181" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="28" t="s">
-        <v>1082</v>
+        <v>1074</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>154</v>
@@ -22275,16 +22301,16 @@
         <v>38</v>
       </c>
       <c r="H181" s="6" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="I181" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J181" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K181" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L181" s="29" t="n">
         <v>4</v>
@@ -22299,7 +22325,7 @@
         <v>630</v>
       </c>
       <c r="P181" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q181" s="6"/>
       <c r="R181" s="6"/>
@@ -22309,7 +22335,7 @@
         <v>673</v>
       </c>
       <c r="V181" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W181" s="6"/>
       <c r="X181" s="6"/>
@@ -22318,7 +22344,7 @@
       <c r="AA181" s="6"/>
       <c r="AB181" s="6"/>
       <c r="AC181" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD181" s="30" t="s">
         <v>208</v>
@@ -22346,10 +22372,10 @@
         <v>1084</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>154</v>
@@ -22367,13 +22393,13 @@
         <v>1085</v>
       </c>
       <c r="I182" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J182" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K182" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L182" s="29" t="n">
         <v>4</v>
@@ -22388,7 +22414,7 @@
         <v>630</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -22398,7 +22424,7 @@
         <v>673</v>
       </c>
       <c r="V182" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W182" s="6"/>
       <c r="X182" s="6"/>
@@ -22407,7 +22433,7 @@
       <c r="AA182" s="6"/>
       <c r="AB182" s="6"/>
       <c r="AC182" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD182" s="30" t="s">
         <v>208</v>
@@ -22435,10 +22461,10 @@
         <v>1086</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>154</v>
@@ -22456,13 +22482,13 @@
         <v>1087</v>
       </c>
       <c r="I183" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J183" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K183" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L183" s="29" t="n">
         <v>4</v>
@@ -22477,7 +22503,7 @@
         <v>630</v>
       </c>
       <c r="P183" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q183" s="6"/>
       <c r="R183" s="6"/>
@@ -22487,7 +22513,7 @@
         <v>673</v>
       </c>
       <c r="V183" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W183" s="6"/>
       <c r="X183" s="6"/>
@@ -22496,7 +22522,7 @@
       <c r="AA183" s="6"/>
       <c r="AB183" s="6"/>
       <c r="AC183" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD183" s="30" t="s">
         <v>208</v>
@@ -22524,10 +22550,10 @@
         <v>1088</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>154</v>
@@ -22545,13 +22571,13 @@
         <v>1089</v>
       </c>
       <c r="I184" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J184" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K184" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L184" s="29" t="n">
         <v>4</v>
@@ -22566,7 +22592,7 @@
         <v>630</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -22576,7 +22602,7 @@
         <v>673</v>
       </c>
       <c r="V184" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W184" s="6"/>
       <c r="X184" s="6"/>
@@ -22585,7 +22611,7 @@
       <c r="AA184" s="6"/>
       <c r="AB184" s="6"/>
       <c r="AC184" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD184" s="30" t="s">
         <v>208</v>
@@ -22613,10 +22639,10 @@
         <v>1090</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>154</v>
@@ -22634,13 +22660,13 @@
         <v>1091</v>
       </c>
       <c r="I185" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J185" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K185" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L185" s="29" t="n">
         <v>4</v>
@@ -22655,7 +22681,7 @@
         <v>630</v>
       </c>
       <c r="P185" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q185" s="6"/>
       <c r="R185" s="6"/>
@@ -22665,7 +22691,7 @@
         <v>673</v>
       </c>
       <c r="V185" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W185" s="6"/>
       <c r="X185" s="6"/>
@@ -22674,7 +22700,7 @@
       <c r="AA185" s="6"/>
       <c r="AB185" s="6"/>
       <c r="AC185" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD185" s="30" t="s">
         <v>208</v>
@@ -22702,10 +22728,10 @@
         <v>1092</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>154</v>
@@ -22723,13 +22749,13 @@
         <v>1093</v>
       </c>
       <c r="I186" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J186" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K186" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L186" s="29" t="n">
         <v>4</v>
@@ -22744,7 +22770,7 @@
         <v>630</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -22754,7 +22780,7 @@
         <v>673</v>
       </c>
       <c r="V186" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W186" s="6"/>
       <c r="X186" s="6"/>
@@ -22763,7 +22789,7 @@
       <c r="AA186" s="6"/>
       <c r="AB186" s="6"/>
       <c r="AC186" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD186" s="30" t="s">
         <v>208</v>
@@ -22791,10 +22817,10 @@
         <v>1094</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>154</v>
@@ -22812,13 +22838,13 @@
         <v>1095</v>
       </c>
       <c r="I187" s="6" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="J187" s="6" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="K187" s="6" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="L187" s="29" t="n">
         <v>4</v>
@@ -22833,7 +22859,7 @@
         <v>630</v>
       </c>
       <c r="P187" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="Q187" s="6"/>
       <c r="R187" s="6"/>
@@ -22843,7 +22869,7 @@
         <v>673</v>
       </c>
       <c r="V187" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="W187" s="6"/>
       <c r="X187" s="6"/>
@@ -22852,7 +22878,7 @@
       <c r="AA187" s="6"/>
       <c r="AB187" s="6"/>
       <c r="AC187" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="AD187" s="30" t="s">
         <v>208</v>
@@ -22880,10 +22906,10 @@
         <v>1096</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>1097</v>
+        <v>1075</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>1098</v>
+        <v>1076</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>154</v>
@@ -22898,45 +22924,51 @@
         <v>38</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="I188" s="6" t="s">
-        <v>1100</v>
+        <v>1078</v>
       </c>
       <c r="J188" s="6" t="s">
-        <v>1101</v>
+        <v>1079</v>
       </c>
       <c r="K188" s="6" t="s">
-        <v>1102</v>
+        <v>1080</v>
       </c>
       <c r="L188" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M188" s="6" t="s">
-        <v>1103</v>
+        <v>628</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>1104</v>
+        <v>629</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>1105</v>
+        <v>630</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>1106</v>
+        <v>1081</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
       <c r="S188" s="6"/>
       <c r="T188" s="6"/>
-      <c r="U188" s="6"/>
-      <c r="V188" s="6"/>
+      <c r="U188" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="V188" s="6" t="s">
+        <v>1082</v>
+      </c>
       <c r="W188" s="6"/>
       <c r="X188" s="6"/>
       <c r="Y188" s="6"/>
       <c r="Z188" s="6"/>
       <c r="AA188" s="6"/>
       <c r="AB188" s="6"/>
-      <c r="AC188" s="6"/>
+      <c r="AC188" s="6" t="s">
+        <v>1083</v>
+      </c>
       <c r="AD188" s="30" t="s">
         <v>208</v>
       </c>
@@ -22960,13 +22992,13 @@
     </row>
     <row r="189" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="28" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>154</v>
@@ -22981,31 +23013,31 @@
         <v>38</v>
       </c>
       <c r="H189" s="6" t="s">
-        <v>1108</v>
+        <v>1101</v>
       </c>
       <c r="I189" s="6" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="J189" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="K189" s="6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="L189" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M189" s="6" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="N189" s="6" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="O189" s="6" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="P189" s="6" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="Q189" s="6"/>
       <c r="R189" s="6"/>
@@ -23046,10 +23078,10 @@
         <v>1109</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>154</v>
@@ -23067,28 +23099,28 @@
         <v>1110</v>
       </c>
       <c r="I190" s="6" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="J190" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="K190" s="6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="L190" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M190" s="6" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="Q190" s="6"/>
       <c r="R190" s="6"/>
@@ -23129,10 +23161,10 @@
         <v>1111</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>154</v>
@@ -23150,28 +23182,28 @@
         <v>1112</v>
       </c>
       <c r="I191" s="6" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="J191" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="K191" s="6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="L191" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M191" s="6" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="N191" s="6" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="O191" s="6" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="P191" s="6" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="Q191" s="6"/>
       <c r="R191" s="6"/>
@@ -23212,10 +23244,10 @@
         <v>1113</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>154</v>
@@ -23233,28 +23265,28 @@
         <v>1114</v>
       </c>
       <c r="I192" s="6" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="J192" s="6" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="K192" s="6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="L192" s="29" t="n">
         <v>4</v>
       </c>
       <c r="M192" s="6" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -23290,9 +23322,92 @@
         <v>Awaiting response</v>
       </c>
     </row>
+    <row r="193" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="28" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B193" s="6" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D193" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E193" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="F193" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="G193" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="H193" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I193" s="6" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J193" s="6" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K193" s="6" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L193" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M193" s="6" t="s">
+        <v>1105</v>
+      </c>
+      <c r="N193" s="6" t="s">
+        <v>1106</v>
+      </c>
+      <c r="O193" s="6" t="s">
+        <v>1107</v>
+      </c>
+      <c r="P193" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="Q193" s="6"/>
+      <c r="R193" s="6"/>
+      <c r="S193" s="6"/>
+      <c r="T193" s="6"/>
+      <c r="U193" s="6"/>
+      <c r="V193" s="6"/>
+      <c r="W193" s="6"/>
+      <c r="X193" s="6"/>
+      <c r="Y193" s="6"/>
+      <c r="Z193" s="6"/>
+      <c r="AA193" s="6"/>
+      <c r="AB193" s="6"/>
+      <c r="AC193" s="6"/>
+      <c r="AD193" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE193" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="AF193" s="31"/>
+      <c r="AG193" s="32"/>
+      <c r="AH193" s="31"/>
+      <c r="AI193" s="32"/>
+      <c r="AJ193" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="AK193" s="34"/>
+      <c r="AL193" s="34"/>
+      <c r="AM193" s="35"/>
+      <c r="AN193" s="36" t="str">
+        <f aca="false">IF(AD193&lt;&gt;"Y","Out of scope",IF(AF193="","Awaiting response",IF(AND(OR(AF193="Yes",AF193="Partial"),AG193=""),"No detail: treat as unanswered",IF(AND(AF193="Yes",AI193=""),"No evidence link",IF(AND(AJ193="Gap",OR(AL193="",AM193="")),"Gap needs owner and due date","OK")))))</f>
+        <v>Awaiting response</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:AN192"/>
-  <conditionalFormatting sqref="AJ5:AJ192">
+  <autoFilter ref="A4:AN193"/>
+  <conditionalFormatting sqref="AJ5:AJ193">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>"Pending"</formula>
     </cfRule>
@@ -23309,7 +23424,7 @@
       <formula>"Not Applicable"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN5:AN192">
+  <conditionalFormatting sqref="AN5:AN193">
     <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>"No detail: treat as unanswered"</formula>
     </cfRule>
@@ -23324,35 +23439,35 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="8">
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AD5:AD192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AD5:AD193" type="list">
       <formula1>Lists!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AE5:AE192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AE5:AE193" type="list">
       <formula1>Lists!$A$2:$A$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AF5:AF192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AF5:AF193" type="list">
       <formula1>Lists!$D$2:$D$5</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AH5:AH192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AH5:AH193" type="list">
       <formula1>Lists!$F$2:$F$14</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AJ5:AJ192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AJ5:AJ193" type="list">
       <formula1>Lists!$E$2:$E$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F5:F192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F5:F193" type="list">
       <formula1>Lists!$B$2:$B$6</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G192" type="list">
+    <dataValidation allowBlank="true" error="Choose a value from the list (edit the Lists sheet to change the options)." errorStyle="warning" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G193" type="list">
       <formula1>Lists!$C$2:$C$4</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Enter a date (for example 2026-10-17)." errorStyle="warning" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AM5:AM192" type="date">
+    <dataValidation allowBlank="true" error="Enter a date (for example 2026-10-17)." errorStyle="warning" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="AM5:AM193" type="date">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -23387,22 +23502,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="37" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="E1" s="37" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="F1" s="37" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23422,7 +23537,7 @@
         <v>127</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>1121</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23442,7 +23557,7 @@
         <v>128</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23459,7 +23574,7 @@
         <v>129</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>1123</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23473,7 +23588,7 @@
         <v>130</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23484,47 +23599,47 @@
         <v>131</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F7" s="0" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F8" s="0" t="s">
-        <v>1127</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F9" s="0" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F10" s="0" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F11" s="0" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F12" s="0" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F13" s="0" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F14" s="0" t="s">
-        <v>1133</v>
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
